--- a/development/one_file_rosetta_output/SP2293_rosetta.xlsx
+++ b/development/one_file_rosetta_output/SP2293_rosetta.xlsx
@@ -398,14 +398,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1:E233"/>
+  <dimension ref="A1:F233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" bestFit="1" customWidth="1" hidden="false" width="17.711"/>
     <col min="2" max="2" bestFit="1" customWidth="1" hidden="false" width="18.711"/>
     <col min="3" max="3" bestFit="1" customWidth="1" hidden="false" width="16.711"/>
-    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
+    <col min="4" max="4" bestFit="1" customWidth="1" hidden="false" width="7.711"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" hidden="false" width="4.711"/>
+    <col min="6" max="6" bestFit="1" customWidth="1" hidden="false" width="70.711"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -426,10 +427,15 @@
       </c>
       <c r="D1" s="3" t="inlineStr">
         <is>
+          <t>N indels</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
           <t>Example n</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>Indel in context</t>
         </is>
@@ -452,9 +458,12 @@
         </is>
       </c>
       <c r="D2" s="4">
-        <v>1</v>
-      </c>
-      <c r="E2" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E2" s="4">
+        <v>1</v>
+      </c>
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -482,7 +491,10 @@
       <c r="D3" s="4">
         <v>1</v>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="4">
+        <v>1</v>
+      </c>
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -510,7 +522,10 @@
       <c r="D4" s="4">
         <v>1</v>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="4">
+        <v>1</v>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -536,9 +551,12 @@
         </is>
       </c>
       <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E5" s="4">
+        <v>1</v>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -599,9 +617,12 @@
         </is>
       </c>
       <c r="D6" s="4">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4">
+        <v>1</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -662,9 +683,12 @@
         </is>
       </c>
       <c r="D7" s="4">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4">
         <v>2</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -727,7 +751,10 @@
       <c r="D8" s="4">
         <v>3</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="4">
+        <v>3</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -790,7 +817,10 @@
       <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="4">
+        <v>1</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -868,7 +898,10 @@
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="4">
+        <v>1</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -946,7 +979,10 @@
       <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="4">
+        <v>1</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1032,7 +1068,10 @@
       <c r="D12" s="4">
         <v>1</v>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="4">
+        <v>1</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1060,7 +1099,10 @@
       <c r="D13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="4">
+        <v>1</v>
+      </c>
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1153,7 +1195,10 @@
       <c r="D14" s="4">
         <v>1</v>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="4">
+        <v>1</v>
+      </c>
+      <c r="F14" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1181,7 +1226,10 @@
       <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="4">
+        <v>1</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1207,9 +1255,12 @@
         </is>
       </c>
       <c r="D16" s="4">
-        <v>1</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E16" s="4">
+        <v>1</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1235,9 +1286,12 @@
         </is>
       </c>
       <c r="D17" s="4">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E17" s="4">
+        <v>1</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1298,9 +1352,12 @@
         </is>
       </c>
       <c r="D18" s="4">
+        <v>3</v>
+      </c>
+      <c r="E18" s="4">
         <v>2</v>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1363,7 +1420,10 @@
       <c r="D19" s="4">
         <v>1</v>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="4">
+        <v>1</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1391,7 +1451,10 @@
       <c r="D20" s="4">
         <v>1</v>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="4">
+        <v>1</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1454,7 +1517,10 @@
       <c r="D21" s="4">
         <v>1</v>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="4">
+        <v>1</v>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1525,7 +1591,10 @@
       <c r="D22" s="4">
         <v>1</v>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="4">
+        <v>1</v>
+      </c>
+      <c r="F22" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1553,7 +1622,10 @@
       <c r="D23" s="4">
         <v>1</v>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="4">
+        <v>1</v>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1652,9 +1724,12 @@
         </is>
       </c>
       <c r="D24" s="4">
-        <v>1</v>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
+        <v>40</v>
+      </c>
+      <c r="E24" s="4">
+        <v>1</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1708,9 +1783,12 @@
         </is>
       </c>
       <c r="D25" s="4">
+        <v>40</v>
+      </c>
+      <c r="E25" s="4">
         <v>2</v>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1764,9 +1842,12 @@
         </is>
       </c>
       <c r="D26" s="4">
+        <v>40</v>
+      </c>
+      <c r="E26" s="4">
         <v>3</v>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1820,9 +1901,12 @@
         </is>
       </c>
       <c r="D27" s="4">
+        <v>40</v>
+      </c>
+      <c r="E27" s="4">
         <v>4</v>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1876,9 +1960,12 @@
         </is>
       </c>
       <c r="D28" s="4">
+        <v>40</v>
+      </c>
+      <c r="E28" s="4">
         <v>5</v>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -1934,7 +2021,10 @@
       <c r="D29" s="4">
         <v>1</v>
       </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="E29" s="4">
+        <v>1</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -1960,9 +2050,12 @@
         </is>
       </c>
       <c r="D30" s="4">
-        <v>1</v>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
+        <v>37</v>
+      </c>
+      <c r="E30" s="4">
+        <v>1</v>
+      </c>
+      <c r="F30" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2016,9 +2109,12 @@
         </is>
       </c>
       <c r="D31" s="4">
+        <v>37</v>
+      </c>
+      <c r="E31" s="4">
         <v>2</v>
       </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="F31" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2072,9 +2168,12 @@
         </is>
       </c>
       <c r="D32" s="4">
+        <v>37</v>
+      </c>
+      <c r="E32" s="4">
         <v>3</v>
       </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="F32" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2128,9 +2227,12 @@
         </is>
       </c>
       <c r="D33" s="4">
+        <v>37</v>
+      </c>
+      <c r="E33" s="4">
         <v>4</v>
       </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2184,9 +2286,12 @@
         </is>
       </c>
       <c r="D34" s="4">
+        <v>37</v>
+      </c>
+      <c r="E34" s="4">
         <v>5</v>
       </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2240,9 +2345,12 @@
         </is>
       </c>
       <c r="D35" s="4">
-        <v>1</v>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="E35" s="4">
+        <v>1</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2305,7 +2413,10 @@
       <c r="D36" s="4">
         <v>1</v>
       </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="E36" s="4">
+        <v>1</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2331,9 +2442,12 @@
         </is>
       </c>
       <c r="D37" s="4">
-        <v>1</v>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
+        <v>9</v>
+      </c>
+      <c r="E37" s="4">
+        <v>1</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2394,9 +2508,12 @@
         </is>
       </c>
       <c r="D38" s="4">
+        <v>9</v>
+      </c>
+      <c r="E38" s="4">
         <v>2</v>
       </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2457,9 +2574,12 @@
         </is>
       </c>
       <c r="D39" s="4">
+        <v>9</v>
+      </c>
+      <c r="E39" s="4">
         <v>3</v>
       </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="F39" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2520,9 +2640,12 @@
         </is>
       </c>
       <c r="D40" s="4">
+        <v>9</v>
+      </c>
+      <c r="E40" s="4">
         <v>4</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="F40" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2583,9 +2706,12 @@
         </is>
       </c>
       <c r="D41" s="4">
+        <v>9</v>
+      </c>
+      <c r="E41" s="4">
         <v>5</v>
       </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="F41" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2646,9 +2772,12 @@
         </is>
       </c>
       <c r="D42" s="4">
-        <v>1</v>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E42" s="4">
+        <v>1</v>
+      </c>
+      <c r="F42" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2674,9 +2803,12 @@
         </is>
       </c>
       <c r="D43" s="4">
-        <v>1</v>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E43" s="4">
+        <v>1</v>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2745,9 +2877,12 @@
         </is>
       </c>
       <c r="D44" s="4">
+        <v>3</v>
+      </c>
+      <c r="E44" s="4">
         <v>2</v>
       </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="F44" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2818,7 +2953,10 @@
       <c r="D45" s="4">
         <v>1</v>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" s="4">
+        <v>1</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -2896,7 +3034,10 @@
       <c r="D46" s="4">
         <v>1</v>
       </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="E46" s="4">
+        <v>1</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2924,7 +3065,10 @@
       <c r="D47" s="4">
         <v>1</v>
       </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="E47" s="4">
+        <v>1</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -2950,9 +3094,12 @@
         </is>
       </c>
       <c r="D48" s="4">
-        <v>1</v>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E48" s="4">
+        <v>1</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3008,7 +3155,10 @@
       <c r="D49" s="4">
         <v>1</v>
       </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="E49" s="4">
+        <v>1</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3036,7 +3186,10 @@
       <c r="D50" s="4">
         <v>1</v>
       </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="E50" s="4">
+        <v>1</v>
+      </c>
+      <c r="F50" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3064,7 +3217,10 @@
       <c r="D51" s="4">
         <v>1</v>
       </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="E51" s="4">
+        <v>1</v>
+      </c>
+      <c r="F51" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3150,7 +3306,10 @@
       <c r="D52" s="4">
         <v>1</v>
       </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="E52" s="4">
+        <v>1</v>
+      </c>
+      <c r="F52" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3266,7 +3425,10 @@
       <c r="D53" s="4">
         <v>1</v>
       </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="E53" s="4">
+        <v>1</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3380,9 +3542,12 @@
         </is>
       </c>
       <c r="D54" s="4">
-        <v>1</v>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E54" s="4">
+        <v>1</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3408,9 +3573,12 @@
         </is>
       </c>
       <c r="D55" s="4">
-        <v>1</v>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E55" s="4">
+        <v>1</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3466,7 +3634,10 @@
       <c r="D56" s="4">
         <v>2</v>
       </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="E56" s="4">
+        <v>2</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3520,9 +3691,12 @@
         </is>
       </c>
       <c r="D57" s="4">
-        <v>1</v>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E57" s="4">
+        <v>1</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3550,7 +3724,10 @@
       <c r="D58" s="4">
         <v>1</v>
       </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="E58" s="4">
+        <v>1</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3578,7 +3755,10 @@
       <c r="D59" s="4">
         <v>1</v>
       </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="E59" s="4">
+        <v>1</v>
+      </c>
+      <c r="F59" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3649,7 +3829,10 @@
       <c r="D60" s="4">
         <v>1</v>
       </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="E60" s="4">
+        <v>1</v>
+      </c>
+      <c r="F60" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3677,7 +3860,10 @@
       <c r="D61" s="4">
         <v>1</v>
       </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="E61" s="4">
+        <v>1</v>
+      </c>
+      <c r="F61" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3703,9 +3889,12 @@
         </is>
       </c>
       <c r="D62" s="4">
-        <v>1</v>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E62" s="4">
+        <v>1</v>
+      </c>
+      <c r="F62" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3733,7 +3922,10 @@
       <c r="D63" s="4">
         <v>1</v>
       </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="E63" s="4">
+        <v>1</v>
+      </c>
+      <c r="F63" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3796,7 +3988,10 @@
       <c r="D64" s="4">
         <v>1</v>
       </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="E64" s="4">
+        <v>1</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3867,7 +4062,10 @@
       <c r="D65" s="4">
         <v>1</v>
       </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="E65" s="4">
+        <v>1</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -3960,7 +4158,10 @@
       <c r="D66" s="4">
         <v>1</v>
       </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="E66" s="4">
+        <v>1</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -3988,7 +4189,10 @@
       <c r="D67" s="4">
         <v>1</v>
       </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="E67" s="4">
+        <v>1</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4094,9 +4298,12 @@
         </is>
       </c>
       <c r="D68" s="4">
-        <v>1</v>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E68" s="4">
+        <v>1</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4150,9 +4357,12 @@
         </is>
       </c>
       <c r="D69" s="4">
+        <v>3</v>
+      </c>
+      <c r="E69" s="4">
         <v>2</v>
       </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4208,7 +4418,10 @@
       <c r="D70" s="4">
         <v>3</v>
       </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="E70" s="4">
+        <v>3</v>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4264,7 +4477,10 @@
       <c r="D71" s="4">
         <v>1</v>
       </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="E71" s="4">
+        <v>1</v>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4292,7 +4508,10 @@
       <c r="D72" s="4">
         <v>1</v>
       </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="E72" s="4">
+        <v>1</v>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4320,7 +4539,10 @@
       <c r="D73" s="4">
         <v>1</v>
       </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="E73" s="4">
+        <v>1</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4348,7 +4570,10 @@
       <c r="D74" s="4">
         <v>1</v>
       </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="E74" s="4">
+        <v>1</v>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4376,7 +4601,10 @@
       <c r="D75" s="4">
         <v>1</v>
       </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="E75" s="4">
+        <v>1</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4404,7 +4632,10 @@
       <c r="D76" s="4">
         <v>1</v>
       </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="E76" s="4">
+        <v>1</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4475,7 +4706,10 @@
       <c r="D77" s="4">
         <v>1</v>
       </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="E77" s="4">
+        <v>1</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4561,7 +4795,10 @@
       <c r="D78" s="4">
         <v>1</v>
       </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="E78" s="4">
+        <v>1</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4589,7 +4826,10 @@
       <c r="D79" s="4">
         <v>1</v>
       </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="E79" s="4">
+        <v>1</v>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4658,9 +4898,12 @@
         </is>
       </c>
       <c r="D80" s="4">
-        <v>1</v>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E80" s="4">
+        <v>1</v>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4738,7 +4981,10 @@
       <c r="D81" s="4">
         <v>2</v>
       </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="E81" s="4">
+        <v>2</v>
+      </c>
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4814,9 +5060,12 @@
         </is>
       </c>
       <c r="D82" s="4">
-        <v>1</v>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E82" s="4">
+        <v>1</v>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -4900,9 +5149,12 @@
         </is>
       </c>
       <c r="D83" s="4">
-        <v>1</v>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E83" s="4">
+        <v>1</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4930,7 +5182,10 @@
       <c r="D84" s="4">
         <v>1</v>
       </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="E84" s="4">
+        <v>1</v>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -4956,9 +5211,12 @@
         </is>
       </c>
       <c r="D85" s="4">
-        <v>1</v>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E85" s="4">
+        <v>1</v>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5051,7 +5309,10 @@
       <c r="D86" s="4">
         <v>1</v>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E86" s="4">
+        <v>1</v>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5150,9 +5411,12 @@
         </is>
       </c>
       <c r="D87" s="4">
-        <v>1</v>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="E87" s="4">
+        <v>1</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5251,9 +5515,12 @@
         </is>
       </c>
       <c r="D88" s="4">
+        <v>5</v>
+      </c>
+      <c r="E88" s="4">
         <v>2</v>
       </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5354,7 +5621,10 @@
       <c r="D89" s="4">
         <v>1</v>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E89" s="4">
+        <v>1</v>
+      </c>
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5382,7 +5652,10 @@
       <c r="D90" s="4">
         <v>1</v>
       </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="E90" s="4">
+        <v>1</v>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5408,9 +5681,12 @@
         </is>
       </c>
       <c r="D91" s="4">
-        <v>1</v>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E91" s="4">
+        <v>1</v>
+      </c>
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5526,7 +5802,10 @@
       <c r="D92" s="4">
         <v>1</v>
       </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="E92" s="4">
+        <v>1</v>
+      </c>
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5552,9 +5831,12 @@
         </is>
       </c>
       <c r="D93" s="4">
-        <v>1</v>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="E93" s="4">
+        <v>1</v>
+      </c>
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5668,9 +5950,12 @@
         </is>
       </c>
       <c r="D94" s="4">
+        <v>4</v>
+      </c>
+      <c r="E94" s="4">
         <v>2</v>
       </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5786,7 +6071,10 @@
       <c r="D95" s="4">
         <v>1</v>
       </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="E95" s="4">
+        <v>1</v>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5812,9 +6100,12 @@
         </is>
       </c>
       <c r="D96" s="4">
-        <v>1</v>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E96" s="4">
+        <v>1</v>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5842,7 +6133,10 @@
       <c r="D97" s="4">
         <v>1</v>
       </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="E97" s="4">
+        <v>1</v>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -5868,9 +6162,12 @@
         </is>
       </c>
       <c r="D98" s="4">
-        <v>1</v>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="E98" s="4">
+        <v>1</v>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5931,9 +6228,12 @@
         </is>
       </c>
       <c r="D99" s="4">
+        <v>5</v>
+      </c>
+      <c r="E99" s="4">
         <v>2</v>
       </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="F99" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -5994,9 +6294,12 @@
         </is>
       </c>
       <c r="D100" s="4">
+        <v>5</v>
+      </c>
+      <c r="E100" s="4">
         <v>3</v>
       </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6057,9 +6360,12 @@
         </is>
       </c>
       <c r="D101" s="4">
+        <v>5</v>
+      </c>
+      <c r="E101" s="4">
         <v>4</v>
       </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="F101" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6122,7 +6428,10 @@
       <c r="D102" s="4">
         <v>5</v>
       </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="E102" s="4">
+        <v>5</v>
+      </c>
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6185,7 +6494,10 @@
       <c r="D103" s="4">
         <v>1</v>
       </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="E103" s="4">
+        <v>1</v>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6213,7 +6525,10 @@
       <c r="D104" s="4">
         <v>1</v>
       </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="E104" s="4">
+        <v>1</v>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6289,9 +6604,12 @@
         </is>
       </c>
       <c r="D105" s="4">
-        <v>1</v>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E105" s="4">
+        <v>1</v>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6369,7 +6687,10 @@
       <c r="D106" s="4">
         <v>1</v>
       </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="E106" s="4">
+        <v>1</v>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6453,9 +6774,12 @@
         </is>
       </c>
       <c r="D107" s="4">
-        <v>1</v>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E107" s="4">
+        <v>1</v>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6548,7 +6872,10 @@
       <c r="D108" s="4">
         <v>1</v>
       </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="E108" s="4">
+        <v>1</v>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -6574,9 +6901,12 @@
         </is>
       </c>
       <c r="D109" s="4">
-        <v>1</v>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E109" s="4">
+        <v>1</v>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6675,9 +7005,12 @@
         </is>
       </c>
       <c r="D110" s="4">
-        <v>1</v>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E110" s="4">
+        <v>1</v>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6778,7 +7111,10 @@
       <c r="D111" s="4">
         <v>1</v>
       </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="E111" s="4">
+        <v>1</v>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6879,7 +7215,10 @@
       <c r="D112" s="4">
         <v>1</v>
       </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="E112" s="4">
+        <v>1</v>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -6985,9 +7324,12 @@
         </is>
       </c>
       <c r="D113" s="4">
-        <v>1</v>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="E113" s="4">
+        <v>1</v>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7093,9 +7435,12 @@
         </is>
       </c>
       <c r="D114" s="4">
+        <v>5</v>
+      </c>
+      <c r="E114" s="4">
         <v>2</v>
       </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="F114" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7201,9 +7546,12 @@
         </is>
       </c>
       <c r="D115" s="4">
+        <v>5</v>
+      </c>
+      <c r="E115" s="4">
         <v>3</v>
       </c>
-      <c r="E115" s="6" t="inlineStr">
+      <c r="F115" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7311,7 +7659,10 @@
       <c r="D116" s="4">
         <v>1</v>
       </c>
-      <c r="E116" s="6" t="inlineStr">
+      <c r="E116" s="4">
+        <v>1</v>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7417,9 +7768,12 @@
         </is>
       </c>
       <c r="D117" s="4">
-        <v>1</v>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E117" s="4">
+        <v>1</v>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7533,9 +7887,12 @@
         </is>
       </c>
       <c r="D118" s="4">
+        <v>3</v>
+      </c>
+      <c r="E118" s="4">
         <v>2</v>
       </c>
-      <c r="E118" s="6" t="inlineStr">
+      <c r="F118" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7649,9 +8006,12 @@
         </is>
       </c>
       <c r="D119" s="4">
-        <v>1</v>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E119" s="4">
+        <v>1</v>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7765,9 +8125,12 @@
         </is>
       </c>
       <c r="D120" s="4">
+        <v>3</v>
+      </c>
+      <c r="E120" s="4">
         <v>2</v>
       </c>
-      <c r="E120" s="6" t="inlineStr">
+      <c r="F120" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -7883,7 +8246,10 @@
       <c r="D121" s="4">
         <v>1</v>
       </c>
-      <c r="E121" s="6" t="inlineStr">
+      <c r="E121" s="4">
+        <v>1</v>
+      </c>
+      <c r="F121" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8006,7 +8372,10 @@
       <c r="D122" s="4">
         <v>1</v>
       </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="E122" s="4">
+        <v>1</v>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8129,7 +8498,10 @@
       <c r="D123" s="4">
         <v>1</v>
       </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="E123" s="4">
+        <v>1</v>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -8157,7 +8529,10 @@
       <c r="D124" s="4">
         <v>1</v>
       </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="E124" s="4">
+        <v>1</v>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8211,9 +8586,12 @@
         </is>
       </c>
       <c r="D125" s="4">
-        <v>1</v>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E125" s="4">
+        <v>1</v>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8276,7 +8654,10 @@
       <c r="D126" s="4">
         <v>2</v>
       </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="E126" s="4">
+        <v>2</v>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8339,7 +8720,10 @@
       <c r="D127" s="4">
         <v>1</v>
       </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="E127" s="4">
+        <v>1</v>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8410,7 +8794,10 @@
       <c r="D128" s="4">
         <v>1</v>
       </c>
-      <c r="E128" s="6" t="inlineStr">
+      <c r="E128" s="4">
+        <v>1</v>
+      </c>
+      <c r="F128" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8488,7 +8875,10 @@
       <c r="D129" s="4">
         <v>1</v>
       </c>
-      <c r="E129" s="6" t="inlineStr">
+      <c r="E129" s="4">
+        <v>1</v>
+      </c>
+      <c r="F129" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8587,9 +8977,12 @@
         </is>
       </c>
       <c r="D130" s="4">
-        <v>1</v>
-      </c>
-      <c r="E130" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E130" s="4">
+        <v>1</v>
+      </c>
+      <c r="F130" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8697,7 +9090,10 @@
       <c r="D131" s="4">
         <v>2</v>
       </c>
-      <c r="E131" s="6" t="inlineStr">
+      <c r="E131" s="4">
+        <v>2</v>
+      </c>
+      <c r="F131" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8805,7 +9201,10 @@
       <c r="D132" s="4">
         <v>1</v>
       </c>
-      <c r="E132" s="6" t="inlineStr">
+      <c r="E132" s="4">
+        <v>1</v>
+      </c>
+      <c r="F132" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -8911,9 +9310,12 @@
         </is>
       </c>
       <c r="D133" s="4">
-        <v>1</v>
-      </c>
-      <c r="E133" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E133" s="4">
+        <v>1</v>
+      </c>
+      <c r="F133" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9027,9 +9429,12 @@
         </is>
       </c>
       <c r="D134" s="4">
-        <v>1</v>
-      </c>
-      <c r="E134" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E134" s="4">
+        <v>1</v>
+      </c>
+      <c r="F134" s="6" t="inlineStr">
         <is>
           <r>
             <rPr/>
@@ -9055,9 +9460,12 @@
         </is>
       </c>
       <c r="D135" s="4">
-        <v>1</v>
-      </c>
-      <c r="E135" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E135" s="4">
+        <v>1</v>
+      </c>
+      <c r="F135" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9180,7 +9588,10 @@
       <c r="D136" s="4">
         <v>1</v>
       </c>
-      <c r="E136" s="6" t="inlineStr">
+      <c r="E136" s="4">
+        <v>1</v>
+      </c>
+      <c r="F136" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9236,7 +9647,10 @@
       <c r="D137" s="4">
         <v>1</v>
       </c>
-      <c r="E137" s="6" t="inlineStr">
+      <c r="E137" s="4">
+        <v>1</v>
+      </c>
+      <c r="F137" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9292,7 +9706,10 @@
       <c r="D138" s="4">
         <v>1</v>
       </c>
-      <c r="E138" s="6" t="inlineStr">
+      <c r="E138" s="4">
+        <v>1</v>
+      </c>
+      <c r="F138" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9346,9 +9763,12 @@
         </is>
       </c>
       <c r="D139" s="4">
-        <v>1</v>
-      </c>
-      <c r="E139" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E139" s="4">
+        <v>1</v>
+      </c>
+      <c r="F139" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9402,9 +9822,12 @@
         </is>
       </c>
       <c r="D140" s="4">
+        <v>3</v>
+      </c>
+      <c r="E140" s="4">
         <v>2</v>
       </c>
-      <c r="E140" s="6" t="inlineStr">
+      <c r="F140" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9460,7 +9883,10 @@
       <c r="D141" s="4">
         <v>3</v>
       </c>
-      <c r="E141" s="6" t="inlineStr">
+      <c r="E141" s="4">
+        <v>3</v>
+      </c>
+      <c r="F141" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9514,9 +9940,12 @@
         </is>
       </c>
       <c r="D142" s="4">
-        <v>1</v>
-      </c>
-      <c r="E142" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E142" s="4">
+        <v>1</v>
+      </c>
+      <c r="F142" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9579,7 +10008,10 @@
       <c r="D143" s="4">
         <v>2</v>
       </c>
-      <c r="E143" s="6" t="inlineStr">
+      <c r="E143" s="4">
+        <v>2</v>
+      </c>
+      <c r="F143" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9642,7 +10074,10 @@
       <c r="D144" s="4">
         <v>1</v>
       </c>
-      <c r="E144" s="6" t="inlineStr">
+      <c r="E144" s="4">
+        <v>1</v>
+      </c>
+      <c r="F144" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9705,7 +10140,10 @@
       <c r="D145" s="4">
         <v>1</v>
       </c>
-      <c r="E145" s="6" t="inlineStr">
+      <c r="E145" s="4">
+        <v>1</v>
+      </c>
+      <c r="F145" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9789,9 +10227,12 @@
         </is>
       </c>
       <c r="D146" s="4">
-        <v>1</v>
-      </c>
-      <c r="E146" s="6" t="inlineStr">
+        <v>10</v>
+      </c>
+      <c r="E146" s="4">
+        <v>1</v>
+      </c>
+      <c r="F146" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9852,9 +10293,12 @@
         </is>
       </c>
       <c r="D147" s="4">
+        <v>10</v>
+      </c>
+      <c r="E147" s="4">
         <v>2</v>
       </c>
-      <c r="E147" s="6" t="inlineStr">
+      <c r="F147" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9915,9 +10359,12 @@
         </is>
       </c>
       <c r="D148" s="4">
+        <v>10</v>
+      </c>
+      <c r="E148" s="4">
         <v>3</v>
       </c>
-      <c r="E148" s="6" t="inlineStr">
+      <c r="F148" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -9978,9 +10425,12 @@
         </is>
       </c>
       <c r="D149" s="4">
+        <v>10</v>
+      </c>
+      <c r="E149" s="4">
         <v>4</v>
       </c>
-      <c r="E149" s="6" t="inlineStr">
+      <c r="F149" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10041,9 +10491,12 @@
         </is>
       </c>
       <c r="D150" s="4">
+        <v>10</v>
+      </c>
+      <c r="E150" s="4">
         <v>5</v>
       </c>
-      <c r="E150" s="6" t="inlineStr">
+      <c r="F150" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10104,9 +10557,12 @@
         </is>
       </c>
       <c r="D151" s="4">
+        <v>10</v>
+      </c>
+      <c r="E151" s="4">
         <v>6</v>
       </c>
-      <c r="E151" s="6" t="inlineStr">
+      <c r="F151" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10167,9 +10623,12 @@
         </is>
       </c>
       <c r="D152" s="4">
+        <v>10</v>
+      </c>
+      <c r="E152" s="4">
         <v>7</v>
       </c>
-      <c r="E152" s="6" t="inlineStr">
+      <c r="F152" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10230,9 +10689,12 @@
         </is>
       </c>
       <c r="D153" s="4">
+        <v>10</v>
+      </c>
+      <c r="E153" s="4">
         <v>8</v>
       </c>
-      <c r="E153" s="6" t="inlineStr">
+      <c r="F153" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10293,9 +10755,12 @@
         </is>
       </c>
       <c r="D154" s="4">
+        <v>10</v>
+      </c>
+      <c r="E154" s="4">
         <v>9</v>
       </c>
-      <c r="E154" s="6" t="inlineStr">
+      <c r="F154" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10358,7 +10823,10 @@
       <c r="D155" s="4">
         <v>10</v>
       </c>
-      <c r="E155" s="6" t="inlineStr">
+      <c r="E155" s="4">
+        <v>10</v>
+      </c>
+      <c r="F155" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10419,9 +10887,12 @@
         </is>
       </c>
       <c r="D156" s="4">
-        <v>1</v>
-      </c>
-      <c r="E156" s="6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="E156" s="4">
+        <v>1</v>
+      </c>
+      <c r="F156" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10490,9 +10961,12 @@
         </is>
       </c>
       <c r="D157" s="4">
+        <v>4</v>
+      </c>
+      <c r="E157" s="4">
         <v>2</v>
       </c>
-      <c r="E157" s="6" t="inlineStr">
+      <c r="F157" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10561,9 +11035,12 @@
         </is>
       </c>
       <c r="D158" s="4">
+        <v>4</v>
+      </c>
+      <c r="E158" s="4">
         <v>3</v>
       </c>
-      <c r="E158" s="6" t="inlineStr">
+      <c r="F158" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10634,7 +11111,10 @@
       <c r="D159" s="4">
         <v>4</v>
       </c>
-      <c r="E159" s="6" t="inlineStr">
+      <c r="E159" s="4">
+        <v>4</v>
+      </c>
+      <c r="F159" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10705,7 +11185,10 @@
       <c r="D160" s="4">
         <v>1</v>
       </c>
-      <c r="E160" s="6" t="inlineStr">
+      <c r="E160" s="4">
+        <v>1</v>
+      </c>
+      <c r="F160" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10783,7 +11266,10 @@
       <c r="D161" s="4">
         <v>1</v>
       </c>
-      <c r="E161" s="6" t="inlineStr">
+      <c r="E161" s="4">
+        <v>1</v>
+      </c>
+      <c r="F161" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -10942,9 +11428,12 @@
         </is>
       </c>
       <c r="D162" s="4">
-        <v>1</v>
-      </c>
-      <c r="E162" s="6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="E162" s="4">
+        <v>1</v>
+      </c>
+      <c r="F162" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11005,9 +11494,12 @@
         </is>
       </c>
       <c r="D163" s="4">
+        <v>4</v>
+      </c>
+      <c r="E163" s="4">
         <v>2</v>
       </c>
-      <c r="E163" s="6" t="inlineStr">
+      <c r="F163" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11068,9 +11560,12 @@
         </is>
       </c>
       <c r="D164" s="4">
+        <v>4</v>
+      </c>
+      <c r="E164" s="4">
         <v>3</v>
       </c>
-      <c r="E164" s="6" t="inlineStr">
+      <c r="F164" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11133,7 +11628,10 @@
       <c r="D165" s="4">
         <v>4</v>
       </c>
-      <c r="E165" s="6" t="inlineStr">
+      <c r="E165" s="4">
+        <v>4</v>
+      </c>
+      <c r="F165" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11196,7 +11694,10 @@
       <c r="D166" s="4">
         <v>1</v>
       </c>
-      <c r="E166" s="6" t="inlineStr">
+      <c r="E166" s="4">
+        <v>1</v>
+      </c>
+      <c r="F166" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11267,7 +11768,10 @@
       <c r="D167" s="4">
         <v>1</v>
       </c>
-      <c r="E167" s="6" t="inlineStr">
+      <c r="E167" s="4">
+        <v>1</v>
+      </c>
+      <c r="F167" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11339,7 +11843,10 @@
       <c r="D168" s="4">
         <v>1</v>
       </c>
-      <c r="E168" s="6" t="inlineStr">
+      <c r="E168" s="4">
+        <v>1</v>
+      </c>
+      <c r="F168" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11440,7 +11947,10 @@
       <c r="D169" s="4">
         <v>1</v>
       </c>
-      <c r="E169" s="6" t="inlineStr">
+      <c r="E169" s="4">
+        <v>1</v>
+      </c>
+      <c r="F169" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11503,7 +12013,10 @@
       <c r="D170" s="4">
         <v>1</v>
       </c>
-      <c r="E170" s="6" t="inlineStr">
+      <c r="E170" s="4">
+        <v>1</v>
+      </c>
+      <c r="F170" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11564,9 +12077,12 @@
         </is>
       </c>
       <c r="D171" s="4">
-        <v>1</v>
-      </c>
-      <c r="E171" s="6" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="E171" s="4">
+        <v>1</v>
+      </c>
+      <c r="F171" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11636,9 +12152,12 @@
         </is>
       </c>
       <c r="D172" s="4">
+        <v>7</v>
+      </c>
+      <c r="E172" s="4">
         <v>2</v>
       </c>
-      <c r="E172" s="6" t="inlineStr">
+      <c r="F172" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11708,9 +12227,12 @@
         </is>
       </c>
       <c r="D173" s="4">
+        <v>7</v>
+      </c>
+      <c r="E173" s="4">
         <v>3</v>
       </c>
-      <c r="E173" s="6" t="inlineStr">
+      <c r="F173" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11780,9 +12302,12 @@
         </is>
       </c>
       <c r="D174" s="4">
+        <v>7</v>
+      </c>
+      <c r="E174" s="4">
         <v>4</v>
       </c>
-      <c r="E174" s="6" t="inlineStr">
+      <c r="F174" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11852,9 +12377,12 @@
         </is>
       </c>
       <c r="D175" s="4">
+        <v>7</v>
+      </c>
+      <c r="E175" s="4">
         <v>5</v>
       </c>
-      <c r="E175" s="6" t="inlineStr">
+      <c r="F175" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11924,9 +12452,12 @@
         </is>
       </c>
       <c r="D176" s="4">
+        <v>7</v>
+      </c>
+      <c r="E176" s="4">
         <v>6</v>
       </c>
-      <c r="E176" s="6" t="inlineStr">
+      <c r="F176" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -11998,7 +12529,10 @@
       <c r="D177" s="4">
         <v>7</v>
       </c>
-      <c r="E177" s="6" t="inlineStr">
+      <c r="E177" s="4">
+        <v>7</v>
+      </c>
+      <c r="F177" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12068,9 +12602,12 @@
         </is>
       </c>
       <c r="D178" s="4">
-        <v>1</v>
-      </c>
-      <c r="E178" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E178" s="4">
+        <v>1</v>
+      </c>
+      <c r="F178" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12140,9 +12677,12 @@
         </is>
       </c>
       <c r="D179" s="4">
+        <v>3</v>
+      </c>
+      <c r="E179" s="4">
         <v>2</v>
       </c>
-      <c r="E179" s="6" t="inlineStr">
+      <c r="F179" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12205,7 +12745,10 @@
       <c r="D180" s="4">
         <v>3</v>
       </c>
-      <c r="E180" s="6" t="inlineStr">
+      <c r="E180" s="4">
+        <v>3</v>
+      </c>
+      <c r="F180" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12275,9 +12818,12 @@
         </is>
       </c>
       <c r="D181" s="4">
-        <v>1</v>
-      </c>
-      <c r="E181" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E181" s="4">
+        <v>1</v>
+      </c>
+      <c r="F181" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12349,7 +12895,10 @@
       <c r="D182" s="4">
         <v>2</v>
       </c>
-      <c r="E182" s="6" t="inlineStr">
+      <c r="E182" s="4">
+        <v>2</v>
+      </c>
+      <c r="F182" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12419,9 +12968,12 @@
         </is>
       </c>
       <c r="D183" s="4">
-        <v>1</v>
-      </c>
-      <c r="E183" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E183" s="4">
+        <v>1</v>
+      </c>
+      <c r="F183" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12505,9 +13057,12 @@
         </is>
       </c>
       <c r="D184" s="4">
+        <v>3</v>
+      </c>
+      <c r="E184" s="4">
         <v>2</v>
       </c>
-      <c r="E184" s="6" t="inlineStr">
+      <c r="F184" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12585,7 +13140,10 @@
       <c r="D185" s="4">
         <v>3</v>
       </c>
-      <c r="E185" s="6" t="inlineStr">
+      <c r="E185" s="4">
+        <v>3</v>
+      </c>
+      <c r="F185" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12656,7 +13214,10 @@
       <c r="D186" s="4">
         <v>1</v>
       </c>
-      <c r="E186" s="6" t="inlineStr">
+      <c r="E186" s="4">
+        <v>1</v>
+      </c>
+      <c r="F186" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12734,7 +13295,10 @@
       <c r="D187" s="4">
         <v>1</v>
       </c>
-      <c r="E187" s="6" t="inlineStr">
+      <c r="E187" s="4">
+        <v>1</v>
+      </c>
+      <c r="F187" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12820,7 +13384,10 @@
       <c r="D188" s="4">
         <v>1</v>
       </c>
-      <c r="E188" s="6" t="inlineStr">
+      <c r="E188" s="4">
+        <v>1</v>
+      </c>
+      <c r="F188" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12911,9 +13478,12 @@
         </is>
       </c>
       <c r="D189" s="4">
-        <v>1</v>
-      </c>
-      <c r="E189" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E189" s="4">
+        <v>1</v>
+      </c>
+      <c r="F189" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -12976,7 +13546,10 @@
       <c r="D190" s="4">
         <v>2</v>
       </c>
-      <c r="E190" s="6" t="inlineStr">
+      <c r="E190" s="4">
+        <v>2</v>
+      </c>
+      <c r="F190" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13039,7 +13612,10 @@
       <c r="D191" s="4">
         <v>1</v>
       </c>
-      <c r="E191" s="6" t="inlineStr">
+      <c r="E191" s="4">
+        <v>1</v>
+      </c>
+      <c r="F191" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13117,7 +13693,10 @@
       <c r="D192" s="4">
         <v>1</v>
       </c>
-      <c r="E192" s="6" t="inlineStr">
+      <c r="E192" s="4">
+        <v>1</v>
+      </c>
+      <c r="F192" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13246,9 +13825,12 @@
         </is>
       </c>
       <c r="D193" s="4">
-        <v>1</v>
-      </c>
-      <c r="E193" s="6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="E193" s="4">
+        <v>1</v>
+      </c>
+      <c r="F193" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13339,9 +13921,12 @@
         </is>
       </c>
       <c r="D194" s="4">
+        <v>4</v>
+      </c>
+      <c r="E194" s="4">
         <v>2</v>
       </c>
-      <c r="E194" s="6" t="inlineStr">
+      <c r="F194" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13470,9 +14055,12 @@
         </is>
       </c>
       <c r="D195" s="4">
+        <v>4</v>
+      </c>
+      <c r="E195" s="4">
         <v>3</v>
       </c>
-      <c r="E195" s="6" t="inlineStr">
+      <c r="F195" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13608,9 +14196,12 @@
         </is>
       </c>
       <c r="D196" s="4">
-        <v>1</v>
-      </c>
-      <c r="E196" s="6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="E196" s="4">
+        <v>1</v>
+      </c>
+      <c r="F196" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13671,9 +14262,12 @@
         </is>
       </c>
       <c r="D197" s="4">
+        <v>4</v>
+      </c>
+      <c r="E197" s="4">
         <v>2</v>
       </c>
-      <c r="E197" s="6" t="inlineStr">
+      <c r="F197" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13734,9 +14328,12 @@
         </is>
       </c>
       <c r="D198" s="4">
+        <v>4</v>
+      </c>
+      <c r="E198" s="4">
         <v>3</v>
       </c>
-      <c r="E198" s="6" t="inlineStr">
+      <c r="F198" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13799,7 +14396,10 @@
       <c r="D199" s="4">
         <v>4</v>
       </c>
-      <c r="E199" s="6" t="inlineStr">
+      <c r="E199" s="4">
+        <v>4</v>
+      </c>
+      <c r="F199" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13862,7 +14462,10 @@
       <c r="D200" s="4">
         <v>1</v>
       </c>
-      <c r="E200" s="6" t="inlineStr">
+      <c r="E200" s="4">
+        <v>1</v>
+      </c>
+      <c r="F200" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -13946,9 +14549,12 @@
         </is>
       </c>
       <c r="D201" s="4">
-        <v>1</v>
-      </c>
-      <c r="E201" s="6" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="E201" s="4">
+        <v>1</v>
+      </c>
+      <c r="F201" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14018,9 +14624,12 @@
         </is>
       </c>
       <c r="D202" s="4">
+        <v>5</v>
+      </c>
+      <c r="E202" s="4">
         <v>2</v>
       </c>
-      <c r="E202" s="6" t="inlineStr">
+      <c r="F202" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14090,9 +14699,12 @@
         </is>
       </c>
       <c r="D203" s="4">
+        <v>5</v>
+      </c>
+      <c r="E203" s="4">
         <v>3</v>
       </c>
-      <c r="E203" s="6" t="inlineStr">
+      <c r="F203" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14162,9 +14774,12 @@
         </is>
       </c>
       <c r="D204" s="4">
+        <v>5</v>
+      </c>
+      <c r="E204" s="4">
         <v>4</v>
       </c>
-      <c r="E204" s="6" t="inlineStr">
+      <c r="F204" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14234,9 +14849,12 @@
         </is>
       </c>
       <c r="D205" s="4">
-        <v>1</v>
-      </c>
-      <c r="E205" s="6" t="inlineStr">
+        <v>4</v>
+      </c>
+      <c r="E205" s="4">
+        <v>1</v>
+      </c>
+      <c r="F205" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14306,9 +14924,12 @@
         </is>
       </c>
       <c r="D206" s="4">
+        <v>4</v>
+      </c>
+      <c r="E206" s="4">
         <v>2</v>
       </c>
-      <c r="E206" s="6" t="inlineStr">
+      <c r="F206" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14378,9 +14999,12 @@
         </is>
       </c>
       <c r="D207" s="4">
+        <v>4</v>
+      </c>
+      <c r="E207" s="4">
         <v>3</v>
       </c>
-      <c r="E207" s="6" t="inlineStr">
+      <c r="F207" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14452,7 +15076,10 @@
       <c r="D208" s="4">
         <v>4</v>
       </c>
-      <c r="E208" s="6" t="inlineStr">
+      <c r="E208" s="4">
+        <v>4</v>
+      </c>
+      <c r="F208" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14522,9 +15149,12 @@
         </is>
       </c>
       <c r="D209" s="4">
-        <v>1</v>
-      </c>
-      <c r="E209" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E209" s="4">
+        <v>1</v>
+      </c>
+      <c r="F209" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14596,7 +15226,10 @@
       <c r="D210" s="4">
         <v>2</v>
       </c>
-      <c r="E210" s="6" t="inlineStr">
+      <c r="E210" s="4">
+        <v>2</v>
+      </c>
+      <c r="F210" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14666,9 +15299,12 @@
         </is>
       </c>
       <c r="D211" s="4">
-        <v>1</v>
-      </c>
-      <c r="E211" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E211" s="4">
+        <v>1</v>
+      </c>
+      <c r="F211" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14740,7 +15376,10 @@
       <c r="D212" s="4">
         <v>2</v>
       </c>
-      <c r="E212" s="6" t="inlineStr">
+      <c r="E212" s="4">
+        <v>2</v>
+      </c>
+      <c r="F212" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14810,9 +15449,12 @@
         </is>
       </c>
       <c r="D213" s="4">
-        <v>1</v>
-      </c>
-      <c r="E213" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E213" s="4">
+        <v>1</v>
+      </c>
+      <c r="F213" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14882,9 +15524,12 @@
         </is>
       </c>
       <c r="D214" s="4">
+        <v>3</v>
+      </c>
+      <c r="E214" s="4">
         <v>2</v>
       </c>
-      <c r="E214" s="6" t="inlineStr">
+      <c r="F214" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -14947,7 +15592,10 @@
       <c r="D215" s="4">
         <v>3</v>
       </c>
-      <c r="E215" s="6" t="inlineStr">
+      <c r="E215" s="4">
+        <v>3</v>
+      </c>
+      <c r="F215" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15017,9 +15665,12 @@
         </is>
       </c>
       <c r="D216" s="4">
-        <v>1</v>
-      </c>
-      <c r="E216" s="6" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="E216" s="4">
+        <v>1</v>
+      </c>
+      <c r="F216" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15091,7 +15742,10 @@
       <c r="D217" s="4">
         <v>2</v>
       </c>
-      <c r="E217" s="6" t="inlineStr">
+      <c r="E217" s="4">
+        <v>2</v>
+      </c>
+      <c r="F217" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15163,7 +15817,10 @@
       <c r="D218" s="4">
         <v>1</v>
       </c>
-      <c r="E218" s="6" t="inlineStr">
+      <c r="E218" s="4">
+        <v>1</v>
+      </c>
+      <c r="F218" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15235,7 +15892,10 @@
       <c r="D219" s="4">
         <v>1</v>
       </c>
-      <c r="E219" s="6" t="inlineStr">
+      <c r="E219" s="4">
+        <v>1</v>
+      </c>
+      <c r="F219" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15307,7 +15967,10 @@
       <c r="D220" s="4">
         <v>1</v>
       </c>
-      <c r="E220" s="6" t="inlineStr">
+      <c r="E220" s="4">
+        <v>1</v>
+      </c>
+      <c r="F220" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15377,9 +16040,12 @@
         </is>
       </c>
       <c r="D221" s="4">
-        <v>1</v>
-      </c>
-      <c r="E221" s="6" t="inlineStr">
+        <v>5</v>
+      </c>
+      <c r="E221" s="4">
+        <v>1</v>
+      </c>
+      <c r="F221" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15449,9 +16115,12 @@
         </is>
       </c>
       <c r="D222" s="4">
+        <v>5</v>
+      </c>
+      <c r="E222" s="4">
         <v>2</v>
       </c>
-      <c r="E222" s="6" t="inlineStr">
+      <c r="F222" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15521,9 +16190,12 @@
         </is>
       </c>
       <c r="D223" s="4">
+        <v>5</v>
+      </c>
+      <c r="E223" s="4">
         <v>3</v>
       </c>
-      <c r="E223" s="6" t="inlineStr">
+      <c r="F223" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15593,9 +16265,12 @@
         </is>
       </c>
       <c r="D224" s="4">
+        <v>5</v>
+      </c>
+      <c r="E224" s="4">
         <v>4</v>
       </c>
-      <c r="E224" s="6" t="inlineStr">
+      <c r="F224" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15665,9 +16340,12 @@
         </is>
       </c>
       <c r="D225" s="4">
-        <v>1</v>
-      </c>
-      <c r="E225" s="6" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="E225" s="4">
+        <v>1</v>
+      </c>
+      <c r="F225" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15737,9 +16415,12 @@
         </is>
       </c>
       <c r="D226" s="4">
+        <v>6</v>
+      </c>
+      <c r="E226" s="4">
         <v>2</v>
       </c>
-      <c r="E226" s="6" t="inlineStr">
+      <c r="F226" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15809,9 +16490,12 @@
         </is>
       </c>
       <c r="D227" s="4">
+        <v>6</v>
+      </c>
+      <c r="E227" s="4">
         <v>3</v>
       </c>
-      <c r="E227" s="6" t="inlineStr">
+      <c r="F227" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15881,9 +16565,12 @@
         </is>
       </c>
       <c r="D228" s="4">
+        <v>6</v>
+      </c>
+      <c r="E228" s="4">
         <v>4</v>
       </c>
-      <c r="E228" s="6" t="inlineStr">
+      <c r="F228" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -15953,9 +16640,12 @@
         </is>
       </c>
       <c r="D229" s="4">
+        <v>6</v>
+      </c>
+      <c r="E229" s="4">
         <v>5</v>
       </c>
-      <c r="E229" s="6" t="inlineStr">
+      <c r="F229" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16027,7 +16717,10 @@
       <c r="D230" s="4">
         <v>6</v>
       </c>
-      <c r="E230" s="6" t="inlineStr">
+      <c r="E230" s="4">
+        <v>6</v>
+      </c>
+      <c r="F230" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16097,9 +16790,12 @@
         </is>
       </c>
       <c r="D231" s="4">
-        <v>1</v>
-      </c>
-      <c r="E231" s="6" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="E231" s="4">
+        <v>1</v>
+      </c>
+      <c r="F231" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16169,9 +16865,12 @@
         </is>
       </c>
       <c r="D232" s="4">
+        <v>3</v>
+      </c>
+      <c r="E232" s="4">
         <v>2</v>
       </c>
-      <c r="E232" s="6" t="inlineStr">
+      <c r="F232" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16243,7 +16942,10 @@
       <c r="D233" s="4">
         <v>1</v>
       </c>
-      <c r="E233" s="6" t="inlineStr">
+      <c r="E233" s="4">
+        <v>1</v>
+      </c>
+      <c r="F233" s="6" t="inlineStr">
         <is>
           <r>
             <rPr>
@@ -16297,121 +16999,159 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="114">
+  <mergeCells count="152">
     <mergeCell ref="A6:A8"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
     <mergeCell ref="A17:A18"/>
     <mergeCell ref="B17:B18"/>
     <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
     <mergeCell ref="A24:A28"/>
     <mergeCell ref="B24:B28"/>
     <mergeCell ref="C24:C28"/>
+    <mergeCell ref="D24:D28"/>
     <mergeCell ref="A30:A34"/>
     <mergeCell ref="B30:B34"/>
     <mergeCell ref="C30:C34"/>
+    <mergeCell ref="D30:D34"/>
     <mergeCell ref="A37:A41"/>
     <mergeCell ref="B37:B41"/>
     <mergeCell ref="C37:C41"/>
+    <mergeCell ref="D37:D41"/>
     <mergeCell ref="A43:A44"/>
     <mergeCell ref="B43:B44"/>
     <mergeCell ref="C43:C44"/>
+    <mergeCell ref="D43:D44"/>
     <mergeCell ref="A55:A56"/>
     <mergeCell ref="B55:B56"/>
     <mergeCell ref="C55:C56"/>
+    <mergeCell ref="D55:D56"/>
     <mergeCell ref="A68:A70"/>
     <mergeCell ref="B68:B70"/>
     <mergeCell ref="C68:C70"/>
+    <mergeCell ref="D68:D70"/>
     <mergeCell ref="A80:A81"/>
     <mergeCell ref="B80:B81"/>
     <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:D81"/>
     <mergeCell ref="A87:A88"/>
     <mergeCell ref="B87:B88"/>
     <mergeCell ref="C87:C88"/>
+    <mergeCell ref="D87:D88"/>
     <mergeCell ref="A93:A94"/>
     <mergeCell ref="B93:B94"/>
     <mergeCell ref="C93:C94"/>
+    <mergeCell ref="D93:D94"/>
     <mergeCell ref="A98:A102"/>
     <mergeCell ref="B98:B102"/>
     <mergeCell ref="C98:C102"/>
+    <mergeCell ref="D98:D102"/>
     <mergeCell ref="A113:A115"/>
     <mergeCell ref="B113:B115"/>
     <mergeCell ref="C113:C115"/>
+    <mergeCell ref="D113:D115"/>
     <mergeCell ref="A117:A118"/>
     <mergeCell ref="B117:B118"/>
     <mergeCell ref="C117:C118"/>
+    <mergeCell ref="D117:D118"/>
     <mergeCell ref="A119:A120"/>
     <mergeCell ref="B119:B120"/>
     <mergeCell ref="C119:C120"/>
+    <mergeCell ref="D119:D120"/>
     <mergeCell ref="A125:A126"/>
     <mergeCell ref="B125:B126"/>
     <mergeCell ref="C125:C126"/>
+    <mergeCell ref="D125:D126"/>
     <mergeCell ref="A130:A131"/>
     <mergeCell ref="B130:B131"/>
     <mergeCell ref="C130:C131"/>
+    <mergeCell ref="D130:D131"/>
     <mergeCell ref="A139:A141"/>
     <mergeCell ref="B139:B141"/>
     <mergeCell ref="C139:C141"/>
+    <mergeCell ref="D139:D141"/>
     <mergeCell ref="A142:A143"/>
     <mergeCell ref="B142:B143"/>
     <mergeCell ref="C142:C143"/>
+    <mergeCell ref="D142:D143"/>
     <mergeCell ref="A146:A155"/>
     <mergeCell ref="B146:B155"/>
     <mergeCell ref="C146:C155"/>
+    <mergeCell ref="D146:D155"/>
     <mergeCell ref="A156:A159"/>
     <mergeCell ref="B156:B159"/>
     <mergeCell ref="C156:C159"/>
+    <mergeCell ref="D156:D159"/>
     <mergeCell ref="A162:A165"/>
     <mergeCell ref="B162:B165"/>
     <mergeCell ref="C162:C165"/>
+    <mergeCell ref="D162:D165"/>
     <mergeCell ref="A171:A177"/>
     <mergeCell ref="B171:B177"/>
     <mergeCell ref="C171:C177"/>
+    <mergeCell ref="D171:D177"/>
     <mergeCell ref="A178:A180"/>
     <mergeCell ref="B178:B180"/>
     <mergeCell ref="C178:C180"/>
+    <mergeCell ref="D178:D180"/>
     <mergeCell ref="A181:A182"/>
     <mergeCell ref="B181:B182"/>
     <mergeCell ref="C181:C182"/>
+    <mergeCell ref="D181:D182"/>
     <mergeCell ref="A183:A185"/>
     <mergeCell ref="B183:B185"/>
     <mergeCell ref="C183:C185"/>
+    <mergeCell ref="D183:D185"/>
     <mergeCell ref="A189:A190"/>
     <mergeCell ref="B189:B190"/>
     <mergeCell ref="C189:C190"/>
+    <mergeCell ref="D189:D190"/>
     <mergeCell ref="A193:A195"/>
     <mergeCell ref="B193:B195"/>
     <mergeCell ref="C193:C195"/>
+    <mergeCell ref="D193:D195"/>
     <mergeCell ref="A196:A199"/>
     <mergeCell ref="B196:B199"/>
     <mergeCell ref="C196:C199"/>
+    <mergeCell ref="D196:D199"/>
     <mergeCell ref="A201:A204"/>
     <mergeCell ref="B201:B204"/>
     <mergeCell ref="C201:C204"/>
+    <mergeCell ref="D201:D204"/>
     <mergeCell ref="A205:A208"/>
     <mergeCell ref="B205:B208"/>
     <mergeCell ref="C205:C208"/>
+    <mergeCell ref="D205:D208"/>
     <mergeCell ref="A209:A210"/>
     <mergeCell ref="B209:B210"/>
     <mergeCell ref="C209:C210"/>
+    <mergeCell ref="D209:D210"/>
     <mergeCell ref="A211:A212"/>
     <mergeCell ref="B211:B212"/>
     <mergeCell ref="C211:C212"/>
+    <mergeCell ref="D211:D212"/>
     <mergeCell ref="A213:A215"/>
     <mergeCell ref="B213:B215"/>
     <mergeCell ref="C213:C215"/>
+    <mergeCell ref="D213:D215"/>
     <mergeCell ref="A216:A217"/>
     <mergeCell ref="B216:B217"/>
     <mergeCell ref="C216:C217"/>
+    <mergeCell ref="D216:D217"/>
     <mergeCell ref="A221:A224"/>
     <mergeCell ref="B221:B224"/>
     <mergeCell ref="C221:C224"/>
+    <mergeCell ref="D221:D224"/>
     <mergeCell ref="A225:A230"/>
     <mergeCell ref="B225:B230"/>
     <mergeCell ref="C225:C230"/>
+    <mergeCell ref="D225:D230"/>
     <mergeCell ref="A231:A232"/>
     <mergeCell ref="B231:B232"/>
     <mergeCell ref="C231:C232"/>
+    <mergeCell ref="D231:D232"/>
   </mergeCells>
   <printOptions gridLines="1" gridLinesSet="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
